--- a/static.xlsx
+++ b/static.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5c2aa0dda8f38b74/デスクトップ/BPUMP/the18/the18/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{4A5B50A9-D421-4192-805D-E50F2B5E85C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF9F9C0B-1615-4A77-9072-6972614C205A}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{4A5B50A9-D421-4192-805D-E50F2B5E85C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DD9B548-E73C-4E24-9A81-4493EE0AB085}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="3" xr2:uid="{5DF35994-0507-450F-86A4-945F99D90598}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="201">
   <si>
     <t>FUN2</t>
     <phoneticPr fontId="1"/>
@@ -760,6 +760,10 @@
   </si>
   <si>
     <t>トクタケ ユノ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タミヤ エイト</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4267,7 +4271,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -4276,8 +4280,8 @@
       <c r="A12" s="9">
         <v>12</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>195</v>
+      <c r="B12" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -4286,8 +4290,8 @@
       <c r="A13" s="9">
         <v>13</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>196</v>
+      <c r="B13" s="15" t="s">
+        <v>195</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9"/>
@@ -4296,8 +4300,8 @@
       <c r="A14" s="9">
         <v>14</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>110</v>
+      <c r="B14" s="9" t="s">
+        <v>196</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
